--- a/download/analyse_belgofish_2024_2026.xlsx
+++ b/download/analyse_belgofish_2024_2026.xlsx
@@ -10,6 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Synthese" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. Detail par ref" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. Mensuel 2025 vs 2026" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. Ventes 2026 mensuel" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,8 +45,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -55,6 +60,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -84,7 +99,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -93,6 +108,8 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1524,4 +1541,396 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>BELGO FISH - Ventes 2026 mois par mois</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Mois</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Volume (t)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>CA (M FCFA)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Nb refs actifs</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Nb clients</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Janvier</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="5" t="inlineStr"/>
+      <c r="E4" s="5" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Fevrier</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="5" t="inlineStr"/>
+      <c r="E5" s="5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Mars</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="5" t="inlineStr"/>
+      <c r="E6" s="5" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Avril</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="5" t="inlineStr"/>
+      <c r="E7" s="5" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Mai</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="5" t="inlineStr"/>
+      <c r="E8" s="5" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Juin</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" s="5" t="inlineStr"/>
+      <c r="E9" s="5" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Juillet</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="5" t="inlineStr"/>
+      <c r="E10" s="5" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Aout</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D11" s="5" t="inlineStr"/>
+      <c r="E11" s="5" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Septembre</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL 2026</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C13" s="7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="7" t="n">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>DETAIL SEPTEMBRE 2026 PAR REFERENCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Volume (t)</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>CA (M FCFA)</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>Nb clients</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Nb agences</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>APCL2</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>BELGO FISH CLARIA 2mm 15kg</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>APCL3</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>BELGO FISH CLARIA 3mm 15kg</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>APCL4.5</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>BELGO FISH CLARIA 4.5mm 15kg</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>APCL6</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>BELGO FISH CLARIA 6mm 15kg</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>APCL8</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>BELGO FISH CLARIA 8mm 15kg</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="7" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="n"/>
+      <c r="C23" s="7" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="D23" s="7" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="E23" s="7" t="n">
+        <v>59</v>
+      </c>
+      <c r="F23" s="7" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>